--- a/data/trans_orig/P04D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30741</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51551</t>
+          <t>52841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255476</t>
+          <t>257099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297049</t>
+          <t>296704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254759</t>
+          <t>256867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293750</t>
+          <t>296010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522141</t>
+          <t>523317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583266</t>
+          <t>584101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138597</t>
+          <t>138639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179972</t>
+          <t>177828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117173</t>
+          <t>115013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>153110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>267192</t>
+          <t>264776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323190</t>
+          <t>323305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>41891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>73923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397903</t>
+          <t>401102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452034</t>
+          <t>451215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361648</t>
+          <t>363833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>408846</t>
+          <t>411880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>777447</t>
+          <t>776806</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>846856</t>
+          <t>848178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202105</t>
+          <t>203861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252846</t>
+          <t>251313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182296</t>
+          <t>180075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228663</t>
+          <t>226381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>396113</t>
+          <t>397079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463136</t>
+          <t>466178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41283</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,82 +1659,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>29618</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19691</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42914</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29618</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19149</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>41865</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>58086</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>44163</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>75476</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>58086</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>43047</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>73665</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>396667</t>
+          <t>394995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>448761</t>
+          <t>450595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399448</t>
+          <t>401767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>454249</t>
+          <t>455330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>814308</t>
+          <t>814878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>888588</t>
+          <t>889468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206281</t>
+          <t>202964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256560</t>
+          <t>257109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228318</t>
+          <t>228465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>284451</t>
+          <t>281447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,47 +1920,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>39,59%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>483087</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>447336</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>519285</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>34,69%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>32,12%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>40,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>483087</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>446284</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>518079</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>40402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36882</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348427</t>
+          <t>352037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400339</t>
+          <t>402149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366993</t>
+          <t>365702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>419492</t>
+          <t>417235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>731623</t>
+          <t>732033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>804018</t>
+          <t>803834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190934</t>
+          <t>189109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>240988</t>
+          <t>238582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>171408</t>
+          <t>172158</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222655</t>
+          <t>222690</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>377889</t>
+          <t>376205</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>452760</t>
+          <t>445306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244642</t>
+          <t>246934</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>286176</t>
+          <t>289550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>267318</t>
+          <t>264208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309182</t>
+          <t>307092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>523700</t>
+          <t>526861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>586081</t>
+          <t>586355</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>122045</t>
+          <t>120905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162394</t>
+          <t>160082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119093</t>
+          <t>117999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160236</t>
+          <t>160673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250356</t>
+          <t>252113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309756</t>
+          <t>308956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>192214</t>
+          <t>192614</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>228021</t>
+          <t>227036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212016</t>
+          <t>212415</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249163</t>
+          <t>248097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>412437</t>
+          <t>414189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>463079</t>
+          <t>463494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>75685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110046</t>
+          <t>109821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89299</t>
+          <t>89461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125511</t>
+          <t>123930</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176491</t>
+          <t>176776</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>224946</t>
+          <t>224457</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>161455</t>
+          <t>161530</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192034</t>
+          <t>192785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>273184</t>
+          <t>273682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>310927</t>
+          <t>309146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>445741</t>
+          <t>443183</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>494111</t>
+          <t>492402</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52474</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81937</t>
+          <t>81585</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>56156</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86740</t>
+          <t>86589</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>114884</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>158238</t>
+          <t>160601</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>120094</t>
+          <t>118571</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>167116</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136385</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>186311</t>
+          <t>187873</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>341272</t>
+          <t>337458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2098435</t>
+          <t>2100521</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2215012</t>
+          <t>2219218</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2233409</t>
+          <t>2238353</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2351145</t>
+          <t>2357039</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4361926</t>
+          <t>4364789</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4531813</t>
+          <t>4534816</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1070530</t>
+          <t>1072620</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1186341</t>
+          <t>1184169</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1046238</t>
+          <t>1045111</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1158167</t>
+          <t>1160957</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2152638</t>
+          <t>2142505</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2315069</t>
+          <t>2305997</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71565</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>104065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144294</t>
+          <t>144314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196619</t>
+          <t>195140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237135</t>
+          <t>237498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183604</t>
+          <t>183764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224025</t>
+          <t>224474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>393273</t>
+          <t>392488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448493</t>
+          <t>448853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116799</t>
+          <t>117121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156059</t>
+          <t>156610</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116229</t>
+          <t>117103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154518</t>
+          <t>154407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245755</t>
+          <t>245040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298945</t>
+          <t>299006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>115330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112886</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168099</t>
+          <t>169276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>221565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>277223</t>
+          <t>275628</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>325684</t>
+          <t>325480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253588</t>
+          <t>250706</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>299078</t>
+          <t>299143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>543519</t>
+          <t>543522</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>607848</t>
+          <t>610671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169792</t>
+          <t>168359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214148</t>
+          <t>215479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170846</t>
+          <t>173566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>214420</t>
+          <t>215476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357625</t>
+          <t>356333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>419208</t>
+          <t>420648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72139</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109924</t>
+          <t>109632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>68018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100037</t>
+          <t>100754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>147862</t>
+          <t>148849</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>198732</t>
+          <t>197533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>330844</t>
+          <t>328827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>383278</t>
+          <t>384144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311245</t>
+          <t>309638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>362828</t>
+          <t>362146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>656200</t>
+          <t>657683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>728121</t>
+          <t>728268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199516</t>
+          <t>195784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250651</t>
+          <t>248306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219481</t>
+          <t>217797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271214</t>
+          <t>268604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430041</t>
+          <t>432682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>500188</t>
+          <t>501428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82042</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123211</t>
+          <t>124677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162891</t>
+          <t>160935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219370</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309895</t>
+          <t>310593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363740</t>
+          <t>364583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>317512</t>
+          <t>318473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370443</t>
+          <t>370695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>645252</t>
+          <t>643925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720010</t>
+          <t>723145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,84%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181143</t>
+          <t>182507</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231751</t>
+          <t>231796</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193990</t>
+          <t>194091</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>244427</t>
+          <t>243476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>390753</t>
+          <t>388078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>459718</t>
+          <t>457420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99188</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62425</t>
+          <t>61434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>94658</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133617</t>
+          <t>132240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180546</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>216949</t>
+          <t>220443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>265342</t>
+          <t>265020</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>224832</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>272384</t>
+          <t>272370</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>459359</t>
+          <t>460274</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>527009</t>
+          <t>522967</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133736</t>
+          <t>135046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180543</t>
+          <t>176928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147884</t>
+          <t>147501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194053</t>
+          <t>194175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>294629</t>
+          <t>293823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>357463</t>
+          <t>357927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>92312</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168491</t>
+          <t>167853</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187208</t>
+          <t>184985</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>226896</t>
+          <t>225770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>365846</t>
+          <t>364695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>418341</t>
+          <t>419485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>77320</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110503</t>
+          <t>109926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96282</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133771</t>
+          <t>134661</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>184761</t>
+          <t>184150</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>235711</t>
+          <t>234036</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55256</t>
+          <t>54575</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>77998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86683</t>
+          <t>84832</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126131</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>140369</t>
+          <t>140394</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169556</t>
+          <t>169330</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>207232</t>
+          <t>209459</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>252558</t>
+          <t>253492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>357927</t>
+          <t>357320</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413390</t>
+          <t>413161</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>71446</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87823</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130365</t>
+          <t>128392</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143880</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>191773</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1732432</t>
+          <t>1738456</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1852822</t>
+          <t>1856736</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1789213</t>
+          <t>1781384</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1905217</t>
+          <t>1905651</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3557527</t>
+          <t>3560251</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3718251</t>
+          <t>3726090</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1006469</t>
+          <t>1013439</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1119401</t>
+          <t>1120759</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1124450</t>
+          <t>1124295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1241712</t>
+          <t>1239099</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2164138</t>
+          <t>2170944</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2329712</t>
+          <t>2326782</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>75141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>46338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104616</t>
+          <t>101119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212728</t>
+          <t>208381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284252</t>
+          <t>280335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183698</t>
+          <t>183111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230220</t>
+          <t>228019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415279</t>
+          <t>414055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499204</t>
+          <t>494961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136425</t>
+          <t>142683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62232</t>
+          <t>64349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102851</t>
+          <t>106465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150069</t>
+          <t>148954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>228745</t>
+          <t>222919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37557</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74065</t>
+          <t>75138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>274903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104211</t>
+          <t>103892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353210</t>
+          <t>356571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248452</t>
+          <t>247778</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>298959</t>
+          <t>299703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>173390</t>
+          <t>169332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>327753</t>
+          <t>325975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>416000</t>
+          <t>420542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>606010</t>
+          <t>610927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>74900</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116808</t>
+          <t>119414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72571</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142168</t>
+          <t>145807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162863</t>
+          <t>163280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247696</t>
+          <t>249398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>52813</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83149</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>40122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71555</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104277</t>
+          <t>101799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149158</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>313830</t>
+          <t>311945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360230</t>
+          <t>357906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>360441</t>
+          <t>363125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>443843</t>
+          <t>441074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689308</t>
+          <t>689014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>790549</t>
+          <t>778386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108321</t>
+          <t>111239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151410</t>
+          <t>151474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111049</t>
+          <t>109870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169759</t>
+          <t>166658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229457</t>
+          <t>234801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307302</t>
+          <t>307816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>107936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>72065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104024</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200400</t>
+          <t>199324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181141</t>
+          <t>161587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555733</t>
+          <t>557266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>421113</t>
+          <t>419682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489744</t>
+          <t>489395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>543105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005123</t>
+          <t>1005267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,8%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233336</t>
+          <t>234411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>673936</t>
+          <t>693074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148416</t>
+          <t>147725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>200273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>410295</t>
+          <t>406618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1004816</t>
+          <t>942806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42556</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50109</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72204</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98181</t>
+          <t>100226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134542</t>
+          <t>135613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>351876</t>
+          <t>352723</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>392815</t>
+          <t>395176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>355160</t>
+          <t>354508</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>387298</t>
+          <t>388385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>721021</t>
+          <t>719429</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>771493</t>
+          <t>773330</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114029</t>
+          <t>113856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>151716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101944</t>
+          <t>101775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129771</t>
+          <t>131505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>224618</t>
+          <t>223579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270990</t>
+          <t>271643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25923</t>
+          <t>26474</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>71367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>105973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221332</t>
+          <t>219870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>250256</t>
+          <t>251460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>404524</t>
+          <t>403069</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>553973</t>
+          <t>548193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>633095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>834764</t>
+          <t>840343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82748</t>
+          <t>82865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110103</t>
+          <t>109822</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36551</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137219</t>
+          <t>138735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97014</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>239909</t>
+          <t>240271</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66467</t>
+          <t>66531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93327</t>
+          <t>94795</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>183538</t>
+          <t>182916</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208455</t>
+          <t>207634</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>297720</t>
+          <t>297971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>324192</t>
+          <t>324081</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>489698</t>
+          <t>488279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>527232</t>
+          <t>524712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>66598</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55545</t>
+          <t>54873</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75917</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>107273</t>
+          <t>108066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136618</t>
+          <t>136469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>284567</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>410684</t>
+          <t>411854</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>360218</t>
+          <t>358228</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>665407</t>
+          <t>630368</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>697379</t>
+          <t>697165</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1047950</t>
+          <t>1008827</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1534447</t>
+          <t>1564751</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2234853</t>
+          <t>2234341</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2344843</t>
+          <t>2339506</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2697045</t>
+          <t>2684967</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4006382</t>
+          <t>4000677</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4768861</t>
+          <t>4785092</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>840456</t>
+          <t>836418</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1655221</t>
+          <t>1618815</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>636803</t>
+          <t>629149</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>859315</t>
+          <t>861343</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1605976</t>
+          <t>1589681</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2581119</t>
+          <t>2486275</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52841</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>254715</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296704</t>
+          <t>296566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256867</t>
+          <t>254230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296010</t>
+          <t>294497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523317</t>
+          <t>521979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584101</t>
+          <t>580793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138639</t>
+          <t>139040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177828</t>
+          <t>180923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>115013</t>
+          <t>115877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>153110</t>
+          <t>154755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>264776</t>
+          <t>268317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323305</t>
+          <t>323984</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>41481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73923</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>401102</t>
+          <t>398607</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451215</t>
+          <t>451056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>363833</t>
+          <t>363481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>411880</t>
+          <t>411225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>776806</t>
+          <t>775745</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>848178</t>
+          <t>846712</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203861</t>
+          <t>201899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251313</t>
+          <t>249951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>182106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226381</t>
+          <t>227666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>397079</t>
+          <t>396399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466178</t>
+          <t>465667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41901</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42914</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>43771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>74808</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>394995</t>
+          <t>396119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>450595</t>
+          <t>446924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>401767</t>
+          <t>403227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455330</t>
+          <t>456223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>814878</t>
+          <t>817801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>889468</t>
+          <t>889417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202964</t>
+          <t>205861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257109</t>
+          <t>254444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228465</t>
+          <t>228052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281447</t>
+          <t>278431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>447336</t>
+          <t>448700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519285</t>
+          <t>517122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13856</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34432</t>
+          <t>37156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40402</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69970</t>
+          <t>68355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352037</t>
+          <t>348939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402149</t>
+          <t>400469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365702</t>
+          <t>366037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>417235</t>
+          <t>416122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732033</t>
+          <t>731806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803834</t>
+          <t>807205</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>189109</t>
+          <t>189764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238582</t>
+          <t>240377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>172158</t>
+          <t>172398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222690</t>
+          <t>222822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376205</t>
+          <t>373316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>445306</t>
+          <t>446474</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33020</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55995</t>
+          <t>57204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>246934</t>
+          <t>247130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>289550</t>
+          <t>288222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264208</t>
+          <t>266406</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>307092</t>
+          <t>309304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526861</t>
+          <t>524250</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>586355</t>
+          <t>584507</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120905</t>
+          <t>120328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160082</t>
+          <t>160960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117999</t>
+          <t>118818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160673</t>
+          <t>160310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252113</t>
+          <t>251403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>308956</t>
+          <t>310929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>192614</t>
+          <t>189671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227036</t>
+          <t>226326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212415</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248097</t>
+          <t>248526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>414189</t>
+          <t>414684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>463494</t>
+          <t>464455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>75464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109821</t>
+          <t>111813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89461</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123930</t>
+          <t>126143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176776</t>
+          <t>175573</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>224457</t>
+          <t>225172</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>37963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>161530</t>
+          <t>161661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192785</t>
+          <t>192447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>273682</t>
+          <t>273750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309146</t>
+          <t>311445</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>443183</t>
+          <t>446888</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>492402</t>
+          <t>492554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51329</t>
+          <t>52391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81585</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56156</t>
+          <t>53443</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86589</t>
+          <t>86856</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114884</t>
+          <t>114143</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>158595</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>118571</t>
+          <t>117106</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>167116</t>
+          <t>167635</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>136385</t>
+          <t>136262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>187873</t>
+          <t>189018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>267675</t>
+          <t>269652</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>337458</t>
+          <t>339063</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2100521</t>
+          <t>2096764</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2219218</t>
+          <t>2214659</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2238353</t>
+          <t>2238515</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2357039</t>
+          <t>2352332</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4364789</t>
+          <t>4362800</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4534816</t>
+          <t>4534267</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1072620</t>
+          <t>1076408</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1184169</t>
+          <t>1189026</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1045111</t>
+          <t>1047579</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1160957</t>
+          <t>1153325</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2142505</t>
+          <t>2148760</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2305997</t>
+          <t>2308780</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84110</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>43453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>70653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>103698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144314</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195140</t>
+          <t>194764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>237632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183764</t>
+          <t>184472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224474</t>
+          <t>221757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>392488</t>
+          <t>393686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448853</t>
+          <t>451458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117121</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156610</t>
+          <t>157222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117103</t>
+          <t>117105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154407</t>
+          <t>154284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245040</t>
+          <t>243949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>299006</t>
+          <t>297810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115330</t>
+          <t>117645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113030</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169276</t>
+          <t>167594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221565</t>
+          <t>218928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>275628</t>
+          <t>277392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>325480</t>
+          <t>325367</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>250706</t>
+          <t>252933</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>299143</t>
+          <t>300971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>543522</t>
+          <t>542193</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>610671</t>
+          <t>611197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168359</t>
+          <t>168466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215479</t>
+          <t>214189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173566</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215476</t>
+          <t>218847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356333</t>
+          <t>353899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420648</t>
+          <t>416730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71924</t>
+          <t>73027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109632</t>
+          <t>108699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68018</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>100073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>148849</t>
+          <t>148560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197533</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>328827</t>
+          <t>330149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384144</t>
+          <t>382575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>309638</t>
+          <t>313562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>362146</t>
+          <t>363546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>657683</t>
+          <t>658292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>728268</t>
+          <t>731219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195784</t>
+          <t>199961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248306</t>
+          <t>247423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217797</t>
+          <t>219094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268604</t>
+          <t>267876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432682</t>
+          <t>430734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>501428</t>
+          <t>498982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>85452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124677</t>
+          <t>123614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68347</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>104107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160935</t>
+          <t>162613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213184</t>
+          <t>216347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>310593</t>
+          <t>309501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>364583</t>
+          <t>362128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318473</t>
+          <t>317261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370695</t>
+          <t>372882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>643925</t>
+          <t>644569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723145</t>
+          <t>720670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182507</t>
+          <t>182556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231796</t>
+          <t>233546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194091</t>
+          <t>195965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243476</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>388078</t>
+          <t>392383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>457420</t>
+          <t>459509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>63096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61434</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94658</t>
+          <t>94728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>132147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181991</t>
+          <t>181869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>220443</t>
+          <t>218866</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>265020</t>
+          <t>266389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>225137</t>
+          <t>224257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>272370</t>
+          <t>272561</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>460274</t>
+          <t>462127</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>522967</t>
+          <t>525441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135046</t>
+          <t>133963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176928</t>
+          <t>178736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147501</t>
+          <t>146658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194175</t>
+          <t>194799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>293823</t>
+          <t>295278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>357927</t>
+          <t>353197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68375</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72438</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>92312</t>
+          <t>91802</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130888</t>
+          <t>130030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>167853</t>
+          <t>168936</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>204932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184985</t>
+          <t>187404</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225770</t>
+          <t>227923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>364695</t>
+          <t>365457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>419485</t>
+          <t>420604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77320</t>
+          <t>77157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109926</t>
+          <t>110894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95362</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134661</t>
+          <t>133007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>184150</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>234036</t>
+          <t>233549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>54486</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>123415</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>140394</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>169330</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>209459</t>
+          <t>208622</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>253492</t>
+          <t>251922</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>357320</t>
+          <t>357604</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413161</t>
+          <t>412269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46415</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71446</t>
+          <t>72393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>90154</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128392</t>
+          <t>132227</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>143880</t>
+          <t>144704</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>192047</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>492038</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>577072</t>
+          <t>577793</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>476803</t>
+          <t>472346</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>562513</t>
+          <t>560787</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>986040</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1118529</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1738456</t>
+          <t>1739624</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1856736</t>
+          <t>1855218</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1781384</t>
+          <t>1785061</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1905651</t>
+          <t>1908236</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3560251</t>
+          <t>3556327</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3726090</t>
+          <t>3722595</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1013439</t>
+          <t>1012908</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1120759</t>
+          <t>1122201</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1124295</t>
+          <t>1128057</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1239099</t>
+          <t>1244241</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2170944</t>
+          <t>2164920</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2326782</t>
+          <t>2328753</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75141</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8528,32 +8528,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>56190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71394</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46338</t>
+          <t>61108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101119</t>
+          <t>119157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -8606,32 +8606,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>249609</t>
+          <t>255591</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208381</t>
+          <t>224082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280335</t>
+          <t>287450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8641,32 +8641,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>206330</t>
+          <t>237318</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>210407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228019</t>
+          <t>260152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8676,32 +8676,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>455939</t>
+          <t>492909</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414055</t>
+          <t>448261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>494961</t>
+          <t>531319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -8719,32 +8719,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104406</t>
+          <t>102918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>78508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142683</t>
+          <t>133752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8754,32 +8754,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81449</t>
+          <t>89213</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64349</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106465</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8789,32 +8789,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>192131</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>148954</t>
+          <t>157830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>222919</t>
+          <t>230855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -8832,17 +8832,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8867,17 +8867,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8902,17 +8902,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8949,32 +8949,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>90475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>65597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>274903</t>
+          <t>81933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9019,32 +9019,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172808</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103892</t>
+          <t>111868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356571</t>
+          <t>163178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -9062,32 +9062,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>274938</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247778</t>
+          <t>278656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299703</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9097,32 +9097,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>316353</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169332</t>
+          <t>293459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>325975</t>
+          <t>337894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9132,32 +9132,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>551319</t>
+          <t>622278</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>420542</t>
+          <t>583780</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>610927</t>
+          <t>652643</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -9175,32 +9175,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94764</t>
+          <t>102612</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>82631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119414</t>
+          <t>128610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9210,32 +9210,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>116749</t>
+          <t>119783</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66908</t>
+          <t>98859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145807</t>
+          <t>140099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9245,32 +9245,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>211513</t>
+          <t>222395</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163280</t>
+          <t>194224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249398</t>
+          <t>255548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9405,102 +9405,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68116</t>
+          <t>86053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>67978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85183</t>
+          <t>105379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>71990</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>58966</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>86712</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>158044</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>135592</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>179573</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>12,72%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>57068</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69786</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>125183</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>101799</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>147869</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -9518,32 +9518,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>336130</t>
+          <t>390214</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>311945</t>
+          <t>365207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>357906</t>
+          <t>415013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>389212</t>
+          <t>388301</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>363125</t>
+          <t>367875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441074</t>
+          <t>408903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9588,32 +9588,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>725342</t>
+          <t>778515</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689014</t>
+          <t>744919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>778386</t>
+          <t>810173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -9631,32 +9631,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>131074</t>
+          <t>143483</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111239</t>
+          <t>120928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151474</t>
+          <t>164907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>145722</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109870</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166658</t>
+          <t>182305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9701,32 +9701,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>276796</t>
+          <t>306385</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234801</t>
+          <t>276798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307816</t>
+          <t>337361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -9744,17 +9744,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>535319</t>
+          <t>619751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>535319</t>
+          <t>619751</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535319</t>
+          <t>619751</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9779,17 +9779,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9814,17 +9814,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1127321</t>
+          <t>1242944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1127321</t>
+          <t>1242944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1127321</t>
+          <t>1242944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9861,32 +9861,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107936</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>102098</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72065</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103449</t>
+          <t>118383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9931,32 +9931,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>161044</t>
+          <t>188371</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101307</t>
+          <t>166466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199324</t>
+          <t>213042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -9974,32 +9974,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>393115</t>
+          <t>426157</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161587</t>
+          <t>399043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557266</t>
+          <t>453756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10009,32 +10009,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>444742</t>
+          <t>444581</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419682</t>
+          <t>424237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489395</t>
+          <t>466313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10044,32 +10044,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>837858</t>
+          <t>870738</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>543105</t>
+          <t>838801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005267</t>
+          <t>905444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>422436</t>
+          <t>188187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234411</t>
+          <t>164419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>693074</t>
+          <t>211903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>179329</t>
+          <t>190207</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147725</t>
+          <t>172784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200273</t>
+          <t>210100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10157,32 +10157,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>601765</t>
+          <t>378394</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>406618</t>
+          <t>346388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>942806</t>
+          <t>409708</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -10200,17 +10200,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10270,17 +10270,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10317,32 +10317,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10352,32 +10352,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60557</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72275</t>
+          <t>88799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10387,32 +10387,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>115909</t>
+          <t>139975</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100226</t>
+          <t>120186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135613</t>
+          <t>159471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -10430,32 +10430,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>372903</t>
+          <t>402108</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>352723</t>
+          <t>377126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>395176</t>
+          <t>424930</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10465,32 +10465,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>372260</t>
+          <t>406677</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>354508</t>
+          <t>387470</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>388385</t>
+          <t>423963</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10500,32 +10500,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>745163</t>
+          <t>808786</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>719429</t>
+          <t>777856</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>773330</t>
+          <t>838830</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -10543,32 +10543,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>132979</t>
+          <t>142105</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113856</t>
+          <t>122404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151716</t>
+          <t>161085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10578,32 +10578,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>115088</t>
+          <t>127335</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>112855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131505</t>
+          <t>143190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10613,32 +10613,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>248067</t>
+          <t>269441</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>223579</t>
+          <t>243773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>271643</t>
+          <t>297362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -10656,17 +10656,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10773,32 +10773,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10808,32 +10808,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71367</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>76450</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>105973</t>
+          <t>105944</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -10886,32 +10886,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>236393</t>
+          <t>260548</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219870</t>
+          <t>243457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>251460</t>
+          <t>277040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10921,32 +10921,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>477060</t>
+          <t>294612</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>403069</t>
+          <t>279220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>548193</t>
+          <t>308361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>713453</t>
+          <t>555160</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>633095</t>
+          <t>533886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>840343</t>
+          <t>577557</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -10999,32 +10999,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>96247</t>
+          <t>104455</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82865</t>
+          <t>91176</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109822</t>
+          <t>119904</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11034,32 +11034,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>87574</t>
+          <t>95664</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>84367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138735</t>
+          <t>107917</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11069,32 +11069,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>183820</t>
+          <t>200119</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92045</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>240271</t>
+          <t>220233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -11112,17 +11112,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11147,17 +11147,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11182,17 +11182,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11229,32 +11229,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11264,32 +11264,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40952</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11299,32 +11299,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>93834</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66531</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94795</t>
+          <t>110758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -11342,32 +11342,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>195833</t>
+          <t>211888</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>182916</t>
+          <t>197503</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>207634</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11377,32 +11377,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>311676</t>
+          <t>335359</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>297971</t>
+          <t>321446</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>324081</t>
+          <t>351837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11412,32 +11412,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>507509</t>
+          <t>547247</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>488279</t>
+          <t>523707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>524712</t>
+          <t>566371</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -11455,32 +11455,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>56500</t>
+          <t>61204</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66598</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11490,32 +11490,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>72522</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>60182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>83790</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11525,32 +11525,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>121382</t>
+          <t>133726</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>108066</t>
+          <t>117809</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136469</t>
+          <t>151788</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -11568,17 +11568,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11603,17 +11603,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11638,17 +11638,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11685,32 +11685,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>276593</t>
+          <t>392665</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>411854</t>
+          <t>481883</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11720,32 +11720,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>358228</t>
+          <t>418692</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>630368</t>
+          <t>492341</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11755,32 +11755,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>697165</t>
+          <t>832728</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1008827</t>
+          <t>947016</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -11798,32 +11798,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1564751</t>
+          <t>2188561</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2234341</t>
+          <t>2316488</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11833,32 +11833,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2339506</t>
+          <t>2372164</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2684967</t>
+          <t>2475473</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11868,32 +11868,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4000677</t>
+          <t>4579598</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4785092</t>
+          <t>4749899</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -11911,32 +11911,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1038405</t>
+          <t>844965</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>836418</t>
+          <t>790926</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1618815</t>
+          <t>905445</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11946,32 +11946,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>790793</t>
+          <t>857626</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>629149</t>
+          <t>813957</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>861343</t>
+          <t>901540</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11981,32 +11981,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1829198</t>
+          <t>1702592</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1589681</t>
+          <t>1631223</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2486275</t>
+          <t>1779453</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -12024,17 +12024,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3458797</t>
+          <t>3531676</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12059,17 +12059,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12094,17 +12094,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7171077</t>
+          <t>7268631</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
